--- a/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS6802_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS6802_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI2"/>
+  <dimension ref="A1:BI3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -909,7 +909,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Air-Way FF6802 (s31, double-pass 2026-10-15, parts.air-way.com/api/series/31, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6802-08-08-NWO-FG (ORFS-p010-t04); FORGED part: Air-Way NON-forged row FF6802-8-8 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length = gen_straight2 FSM_MEAS (Brennan FS2403-08-08); on the forged legs the thread major runs to the end length and steps down to the hex flats (Brennan FS6500 / FS6801 / FS2701-08 forged legs) - the end stands proud of the flats; hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way FF6802 (s31, double-pass 2026-10-15, parts.air-way.com/api/series/31, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6802-08-08-NWO-FG (ORFS-p010-t04); FORGED part: Air-Way NON-forged row FF6802-8-8 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -920,6 +920,211 @@
       <c r="BI2" t="inlineStr">
         <is>
           <t>FS6802-08-08-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FS6802-06-08-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="G3" t="n">
+        <v>75</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.55271</v>
+      </c>
+      <c r="I3" t="n">
+        <v>75</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="W3" t="n">
+        <v>45</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.43251</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>FS6802-06-08-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>ORFS 45 deg Male Face Seal x Adjustable Male ORB Elbow, 3/4-16 (adjustable male ORB) x 11/16-16 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>FS6802</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>3/4-16 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>11/16-16 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Air-Way FF6802 (s31, double-pass 2026-10-15, parts.air-way.com/api/series/31, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6802-06-08-NWO-FG (ORFS-p010-t04); FORGED part: Air-Way NON-forged row FF6802-6-8 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged FF6802-6-8 NWO = Brennan forged FS6802-06-08-NWO-FG p10 on every compared cell (M LGTH ~ L12, N LGTH ~ L13, C HEX ~ S3, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6802 is used only where Brennan FS6802-NWO-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5672 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 1: adjustable stud tip -&gt; washer face 0.54 = L13 - L14 (Air-Way), thread 0.394 = stud - undercut 0.146, tip -&gt; body face 1.03 (FS lock nut 0.41 thick, NWO_FS); leg 1: the corner puck (radius 0.433) reaches 0.033 past the body face (0.400) inside the neck (max 0.166 off the axis vs neck radius 0.375) - as on the 45 deg Brennan forgings</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>FS6802-06-08-NWO-FG</t>
         </is>
       </c>
     </row>

--- a/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS6802_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS6802_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
